--- a/loan_application_forms/042_personal_loan_application_form--loan_application_forms.xlsx
+++ b/loan_application_forms/042_personal_loan_application_form--loan_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Last name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -768,23 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>accept_terms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Accept Terms</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,292 +796,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>accept_terms</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Accept Terms</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>First name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Last name</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>loan_amount</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Loan Amount</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>loan_term</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Loan Term</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>loan_interest_rate</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Loan Interest Rate</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_loan_purpose</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select Loan Purpose</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_other</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Other Loan Purpose</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1324,142 +1071,6 @@
       <c r="C13" t="inlineStr">
         <is>
           <t>Cancel</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>home_improvement</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Home improvement</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>paying_off_debt</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Paying off debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>wedding</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_other_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>home_improvement</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Home improvement</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_other_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>paying_off_debt</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Paying off debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_other_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>wedding</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Wedding</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_loan_purpose_other_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>
